--- a/dugnad/sjekkpakker/OKO-05.xlsx
+++ b/dugnad/sjekkpakker/OKO-05.xlsx
@@ -29,12 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
   <si>
     <t>Sjekkpakke OKO-05: Miljø og energi</t>
   </si>
   <si>
-    <t>Laget 2026-10-27 · 8 påstander · Uregulert KI (arbeidstittel)</t>
+    <t>Laget 2026-10-27 · 9 påstander · Uregulert KI (arbeidstittel)</t>
   </si>
   <si>
     <t>Sjekket av</t>
@@ -172,7 +172,7 @@
     <t>Du kan bruke KI til å finne kilder, oppsummere og peke deg til rett sted i kilden. Men selve sjekken gjør du selv ved å lese originalen. Uten menneskelig verifisering er dugnaden verdiløs.</t>
   </si>
   <si>
-    <t>Privatpersoner navngis aldri.</t>
+    <t>Privatpersoner i privat rolle navngis aldri. Forskere og fagpersoner som uttaler seg offentlig i fagrollen sin, kan navngis.</t>
   </si>
   <si>
     <t>Spørsmål?</t>
@@ -287,6 +287,22 @@
     <t>ikke verifisert · Eksistens (2026-10-25): usikker – Generell beskrivelse; eksakte titler ikke sett. Kandidater: NVE-rapport 2026-17 (kraftårsrapport for 2025 ifølge søket) https://publikasjoner.nve.no/rapport/2026/rapport2026_17.pdf ; NVEs metodenotat om framskriving av datasentre (2026) https://www.nve.no/media/20262/metodenotat-framskriving-datasen</t>
   </si>
   <si>
+    <t>K1206</t>
+  </si>
+  <si>
+    <t>Rybalka og Lied-Endresen (SSB) (2026) – Datasentrene vokser raskt – men hvilke verdier skaper de for Norge? (SSB innsikt 2026/2) · SSB</t>
+  </si>
+  <si>
+    <t>https://www.ssb.no/teknologi-og-innovasjon/informasjons-og-kommunikasjonsteknologi-ikt/artikler/datasentrene-vokser-raskt-men-hvilke-verdier-skaper-de-for-norge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datasentrenes andel vokser raskt: fra om lag 0,5 % av strømforbruket i 2022 til rundt 2 % i 2025, med om lag 35 % årlig vekst. Eksisterende datasentre har fått tildelt 4 350 MW, hvorav 794 MW er i bruk, og 6 833 MW står i Statnetts kø [K1206].
+SSBs nyanse: det er «vanskelig å hevde at næringen alene driver opp strømprisene». Flaskehalsen er kapasiteten i nettet, ikke mangel på energi, men datasentre kan fortrenge annen industri lokalt [K1206].</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-27 (REG-02). Publisert 28.04.2026, endret 20.10.2026.</t>
+  </si>
+  <si>
     <t>OKO-05.P03</t>
   </si>
   <si>
@@ -373,6 +389,12 @@
   </si>
   <si>
     <t>Kraft som brukes i datasentre, kan ikke brukes til å elektrifisere transport, industri og sokkel</t>
+  </si>
+  <si>
+    <t>OKO-05.P09</t>
+  </si>
+  <si>
+    <t>Datasentrenes andel av strømforbruket økte fra om lag 0,5 prosent i 2022 til rundt 2 prosent i 2025</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1272,26 +1294,22 @@
       <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="E6" s="10" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -1305,22 +1323,26 @@
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
+      <c r="A7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="C7" s="9" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -1334,26 +1356,22 @@
       <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -1368,25 +1386,25 @@
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>93</v>
-      </c>
       <c r="D9" s="9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -1401,25 +1419,25 @@
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="E10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1434,25 +1452,25 @@
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="E11" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>111</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -1467,25 +1485,25 @@
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="D12" s="9" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -1498,43 +1516,112 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
     </row>
+    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <mergeCells count="16">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="L3:L6"/>
+    <mergeCell ref="M3:M6"/>
+    <mergeCell ref="N3:N6"/>
+    <mergeCell ref="O3:O6"/>
+    <mergeCell ref="P3:P6"/>
+    <mergeCell ref="Q3:Q6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:Q8"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="H10:H11">
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H12">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H3:H11">
+    <dataValidation type="list" allowBlank="1" sqref="H14">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J10:J12">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H12">
+      <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J10:J14">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J12">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J14">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P12">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P14">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P12">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P14">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1542,7 +1629,9 @@
     <hyperlink ref="E3" r:id="rId1"/>
     <hyperlink ref="E6" r:id="rId2"/>
     <hyperlink ref="E7" r:id="rId3"/>
-    <hyperlink ref="E10" r:id="rId4"/>
+    <hyperlink ref="E8" r:id="rId4"/>
+    <hyperlink ref="E11" r:id="rId5"/>
+    <hyperlink ref="E14" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/dugnad/sjekkpakker/OKO-05.xlsx
+++ b/dugnad/sjekkpakker/OKO-05.xlsx
@@ -20,7 +20,7 @@
     <comment ref="B4" authorId="0">
       <text>
         <r>
-          <t>Kallenavn eller GitHub-navn. Det kan bli stående offentlig i kilderegisteret.</t>
+          <t>Navnet du vil stå med offentlig: fullt navn, kallenavn eller GitHub-navn. Det blir stående i kilderegisteret på GitHub og kan ikke fjernes helt i ettertid.</t>
         </r>
       </text>
     </comment>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="123">
   <si>
     <t>Sjekkpakke OKO-05: Miljø og energi</t>
   </si>
@@ -64,7 +64,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>Les det som er relevant, og sammenlign med «Rapporten sier». Sett «Status» og skriv kort i «Om kilden» hvordan du sjekket og hva som eventuelt avviker.</t>
+    <t>Les det som er relevant, og sammenlign med «Rapporten sier». Sett «Status», og skriv i «Avvik» hvis noe avviker, ligger bak betalingsmur eller er uventet.</t>
+  </si>
+  <si>
+    <t>Er status «verifisert» eller «delvis», skriv i «Hvor i kilden» hvor det står: side (rapport, bok, artikkel), § og ledd (lov), artikkel og nummer (EU-rett), avsnitt (dom) eller overskrift (nettside). Da kan neste person slå rett opp.</t>
   </si>
   <si>
     <t>4</t>
@@ -94,13 +97,13 @@
     <t>verifisert</t>
   </si>
   <si>
-    <t>Du har åpnet primærkilden, og den sier det påstanden bygger på.</t>
+    <t>Du har lest det relevante i primærkilden, og den sier det påstanden bygger på.</t>
   </si>
   <si>
     <t>delvis</t>
   </si>
   <si>
-    <t>Stemmer, men med avvik. Skriv avviket i «Om kilden».</t>
+    <t>Stemmer, men med avvik. Skriv avviket i «Avvik».</t>
   </si>
   <si>
     <t>sekundær</t>
@@ -157,13 +160,13 @@
     <t>A Aktualitet</t>
   </si>
   <si>
-    <t>Er det fortsatt gyldig? 0 utdatert (motbevist, erstattet, loven endret) eller ikke sjekket · 1 usikker gyldighet (feltet har endret seg mye siden, f.eks. studier av eldre KI-modeller) · 2 gyldig, ingen kjent nyere forskning sier noe annet, uansett alder · 3 fersk (gjelder dagens situasjon) eller bekreftet av nyere forskning. Bekreftelsen kan stå i kommentaren.</t>
+    <t>Er det fortsatt gyldig? 0 utdatert (motbevist, erstattet, lovendring) eller ikke sjekket · 1 usikker gyldighet (feltet har endret seg mye siden, f.eks. studier av eldre KI-modeller) · 2 gyldig, ingen kjent nyere forskning sier noe annet, uansett alder · 3 fersk (gjelder dagens situasjon) eller bekreftet av nyere forskning. Bekreftelsen kan stå i kommentaren.</t>
   </si>
   <si>
     <t>Husk</t>
   </si>
   <si>
-    <t>Aldri dikt opp. Tall, datoer og navn tas fra kilden, ikke fra hukommelsen.</t>
+    <t>Ha integritet.</t>
   </si>
   <si>
     <t>Skill mellom «viser», «tyder på» og «antyder», og mellom én studie og konsensus. En påstand kan ha riktig kilde og likevel si mer enn kilden gjør.</t>
@@ -205,13 +208,16 @@
     <t>Status ▾</t>
   </si>
   <si>
+    <t>Hvor i kilden (s., §, art., avsnitt)</t>
+  </si>
+  <si>
     <t>Riktig eller ny lenke / DOI</t>
   </si>
   <si>
     <t>Fagfelle-vurdert ▾</t>
   </si>
   <si>
-    <t>Om kilden: hvordan du sjekket, hva som avviker</t>
+    <t>Avvik / betalingsmur / uventet</t>
   </si>
   <si>
     <t>E ▾</t>
@@ -401,6 +407,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -433,12 +442,17 @@
       <color rgb="FF1F5FA8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -461,7 +475,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -469,36 +483,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -840,256 +884,291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="2" max="2" width="91.45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B5" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+    </row>
+    <row r="7" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="14" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="15" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+    </row>
+    <row r="17" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3" t="s">
+    </row>
+    <row r="19" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="20" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="B20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="B21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="23" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="6" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+    </row>
+    <row r="25" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="B26" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="B28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="30" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="B32" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="3" t="s">
+    <row r="35" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="3" t="s">
+    </row>
+    <row r="37" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="B37" s="13" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1098,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1109,498 +1188,515 @@
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="36" customWidth="1"/>
-    <col min="12" max="16" width="5" customWidth="1"/>
-    <col min="17" max="17" width="40" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="36" customWidth="1"/>
+    <col min="13" max="17" width="5" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" ht="32" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="N1" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="P1" s="15" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="Q1" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="R1" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="9" t="s">
+    </row>
+    <row r="2" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="B2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-    </row>
-    <row r="3" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="C2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="D2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="E2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+    </row>
+    <row r="3" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="B3" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-    </row>
-    <row r="4" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9" t="s">
+      <c r="F3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="G3" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="D4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9" t="s">
+      <c r="E4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="G4" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
+      <c r="D5" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+    </row>
+    <row r="6" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="D6" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="E6" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-    </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="F6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="G6" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="10" t="s">
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="D7" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="E7" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="F7" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+    </row>
+    <row r="8" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="D8" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="E8" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="F8" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="B9" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="C9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="D9" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="E9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="G9" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="D10" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="E10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+    </row>
+    <row r="11" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="B11" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="C11" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="D11" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="E11" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="F11" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="G11" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+    </row>
+    <row r="12" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="B12" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="C12" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="D12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="E12" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="G12" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B13" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="C13" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="D14" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="E14" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
+      <c r="F14" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R14"/>
   <mergeCells count="16">
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B3:B6"/>
-    <mergeCell ref="L3:L6"/>
     <mergeCell ref="M3:M6"/>
     <mergeCell ref="N3:N6"/>
     <mergeCell ref="O3:O6"/>
     <mergeCell ref="P3:P6"/>
     <mergeCell ref="Q3:Q6"/>
+    <mergeCell ref="R3:R6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="O7:O8"/>
     <mergeCell ref="P7:P8"/>
     <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" sqref="H10:H12">
@@ -1612,16 +1708,16 @@
     <dataValidation type="list" allowBlank="1" sqref="H3:H12">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J10:J14">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K14">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J14">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K14">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P14">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M10:Q14">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P14">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:Q14">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
